--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120216601</v>
+        <v>120215290</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492785</v>
+        <v>492789</v>
       </c>
       <c r="R2" t="n">
-        <v>6701271</v>
+        <v>6701247</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +758,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120214458</v>
+        <v>120216396</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +803,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492746</v>
+        <v>492762</v>
       </c>
       <c r="R3" t="n">
-        <v>6701285</v>
+        <v>6701287</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,21 +869,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,26 +882,46 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120215561</v>
+        <v>120214353</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,48 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492762</v>
+        <v>492819</v>
       </c>
       <c r="R4" t="n">
-        <v>6701287</v>
+        <v>6701324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +991,9 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120214431</v>
+        <v>120214376</v>
       </c>
       <c r="B5" t="n">
-        <v>100171</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,24 +1041,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -1086,7 +1080,7 @@
         <v>6701324</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,11 +1107,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1126,6 +1130,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1142,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120214376</v>
+        <v>120213970</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,50 +1163,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492819</v>
+        <v>492816</v>
       </c>
       <c r="R6" t="n">
-        <v>6701324</v>
+        <v>6701297</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,19 +1224,9 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120214276</v>
+        <v>120214458</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,46 +1274,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492828</v>
+        <v>492746</v>
       </c>
       <c r="R7" t="n">
-        <v>6701317</v>
+        <v>6701285</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,22 +1358,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120216396</v>
+        <v>120215561</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,31 +1386,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1471,11 +1457,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1488,21 +1484,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1520,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120214353</v>
+        <v>120214276</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,37 +1517,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492819</v>
+        <v>492828</v>
       </c>
       <c r="R9" t="n">
-        <v>6701324</v>
+        <v>6701317</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1593,11 +1583,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1606,11 +1606,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1627,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120213970</v>
+        <v>120214431</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,25 +1634,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492816</v>
+        <v>492819</v>
       </c>
       <c r="R10" t="n">
-        <v>6701297</v>
+        <v>6701324</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1713,11 +1708,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1734,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120215290</v>
+        <v>120216601</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,42 +1740,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492789</v>
+        <v>492785</v>
       </c>
       <c r="R11" t="n">
-        <v>6701247</v>
+        <v>6701271</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,11 +1802,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1830,6 +1810,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120215290</v>
+        <v>120214458</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492789</v>
+        <v>492746</v>
       </c>
       <c r="R2" t="n">
-        <v>6701247</v>
+        <v>6701285</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,14 +748,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120216396</v>
+        <v>120215561</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -869,11 +874,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -886,21 +901,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120214353</v>
+        <v>120214431</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,7 +964,7 @@
         <v>6701324</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,11 +1004,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120214376</v>
+        <v>120214353</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1032,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -1107,19 +1093,9 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120213970</v>
+        <v>120216396</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,37 +1143,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492816</v>
+        <v>492762</v>
       </c>
       <c r="R6" t="n">
-        <v>6701297</v>
+        <v>6701287</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,6 +1226,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120214458</v>
+        <v>120213970</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492746</v>
+        <v>492816</v>
       </c>
       <c r="R7" t="n">
-        <v>6701285</v>
+        <v>6701297</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,21 +1331,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1354,26 +1344,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120215561</v>
+        <v>120214276</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1381,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1424,13 +1414,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492762</v>
+        <v>492828</v>
       </c>
       <c r="R8" t="n">
-        <v>6701287</v>
+        <v>6701317</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,11 +1470,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1501,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120214276</v>
+        <v>120216601</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,46 +1502,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492828</v>
+        <v>492785</v>
       </c>
       <c r="R9" t="n">
-        <v>6701317</v>
+        <v>6701271</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,21 +1559,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1606,6 +1572,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1622,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120214431</v>
+        <v>120215290</v>
       </c>
       <c r="B10" t="n">
-        <v>100194</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,38 +1620,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492819</v>
+        <v>492789</v>
       </c>
       <c r="R10" t="n">
-        <v>6701324</v>
+        <v>6701247</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,6 +1689,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120216601</v>
+        <v>120214376</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,38 +1732,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492785</v>
+        <v>492819</v>
       </c>
       <c r="R11" t="n">
-        <v>6701271</v>
+        <v>6701324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,11 +1802,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1814,21 +1829,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120213970</v>
+        <v>120214276</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,37 +1274,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492816</v>
+        <v>492828</v>
       </c>
       <c r="R7" t="n">
-        <v>6701297</v>
+        <v>6701317</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,11 +1340,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1344,11 +1363,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1365,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120214276</v>
+        <v>120213970</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,46 +1395,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492828</v>
+        <v>492816</v>
       </c>
       <c r="R8" t="n">
-        <v>6701317</v>
+        <v>6701297</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,21 +1452,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1470,6 +1465,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120215290</v>
+        <v>120214376</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,20 +1620,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1641,10 +1641,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1653,13 +1657,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492789</v>
+        <v>492819</v>
       </c>
       <c r="R10" t="n">
-        <v>6701247</v>
+        <v>6701324</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,14 +1690,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,6 +1713,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1720,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120214376</v>
+        <v>120215290</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,20 +1746,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1753,14 +1767,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,13 +1779,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492819</v>
+        <v>492789</v>
       </c>
       <c r="R11" t="n">
-        <v>6701324</v>
+        <v>6701247</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,19 +1812,14 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:49</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,11 +1830,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120214458</v>
+        <v>120214431</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492746</v>
+        <v>492819</v>
       </c>
       <c r="R2" t="n">
-        <v>6701285</v>
+        <v>6701324</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -918,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120214431</v>
+        <v>120214458</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492819</v>
+        <v>492746</v>
       </c>
       <c r="R4" t="n">
-        <v>6701324</v>
+        <v>6701285</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,9 +981,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120214353</v>
+        <v>120216601</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492819</v>
+        <v>492785</v>
       </c>
       <c r="R5" t="n">
-        <v>6701324</v>
+        <v>6701271</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,6 +1110,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1127,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120216396</v>
+        <v>120214276</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,31 +1158,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492762</v>
+        <v>492828</v>
       </c>
       <c r="R6" t="n">
-        <v>6701287</v>
+        <v>6701317</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,11 +1224,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1222,26 +1247,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1258,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120214276</v>
+        <v>120214353</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,46 +1279,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492828</v>
+        <v>492819</v>
       </c>
       <c r="R7" t="n">
-        <v>6701317</v>
+        <v>6701324</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,21 +1336,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1363,6 +1349,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1379,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120213970</v>
+        <v>120214376</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,41 +1382,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492816</v>
+        <v>492819</v>
       </c>
       <c r="R8" t="n">
-        <v>6701297</v>
+        <v>6701324</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,9 +1452,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120216601</v>
+        <v>120213970</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,21 +1512,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492785</v>
+        <v>492816</v>
       </c>
       <c r="R9" t="n">
-        <v>6701271</v>
+        <v>6701297</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,21 +1586,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120214376</v>
+        <v>120216396</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,35 +1615,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1657,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492819</v>
+        <v>492762</v>
       </c>
       <c r="R10" t="n">
-        <v>6701324</v>
+        <v>6701287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,21 +1685,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1717,6 +1702,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120214431</v>
+        <v>120215290</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492819</v>
+        <v>492789</v>
       </c>
       <c r="R2" t="n">
-        <v>6701324</v>
+        <v>6701247</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120215561</v>
+        <v>120214276</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +803,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -831,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492762</v>
+        <v>492828</v>
       </c>
       <c r="R3" t="n">
-        <v>6701287</v>
+        <v>6701317</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,11 +892,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120214458</v>
+        <v>120213970</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492746</v>
+        <v>492816</v>
       </c>
       <c r="R4" t="n">
-        <v>6701285</v>
+        <v>6701297</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,21 +981,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1004,26 +994,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120216601</v>
+        <v>120216396</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1031,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492785</v>
+        <v>492762</v>
       </c>
       <c r="R5" t="n">
-        <v>6701271</v>
+        <v>6701287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120214276</v>
+        <v>120214431</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,50 +1158,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492828</v>
+        <v>492819</v>
       </c>
       <c r="R6" t="n">
-        <v>6701317</v>
+        <v>6701324</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,19 +1219,9 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120214353</v>
+        <v>120214376</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,28 +1260,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -1336,9 +1330,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120214376</v>
+        <v>120214458</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,50 +1386,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492819</v>
+        <v>492746</v>
       </c>
       <c r="R8" t="n">
-        <v>6701324</v>
+        <v>6701285</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,31 +1470,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120213970</v>
+        <v>120215561</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,37 +1502,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492816</v>
+        <v>492762</v>
       </c>
       <c r="R9" t="n">
-        <v>6701297</v>
+        <v>6701287</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,9 +1573,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120216396</v>
+        <v>120214353</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,43 +1633,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492762</v>
+        <v>492819</v>
       </c>
       <c r="R10" t="n">
-        <v>6701287</v>
+        <v>6701324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,21 +1707,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1734,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120215290</v>
+        <v>120216601</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,42 +1740,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492789</v>
+        <v>492785</v>
       </c>
       <c r="R11" t="n">
-        <v>6701247</v>
+        <v>6701271</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,11 +1802,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1830,6 +1810,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120213970</v>
+        <v>120214353</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492816</v>
+        <v>492819</v>
       </c>
       <c r="R4" t="n">
-        <v>6701297</v>
+        <v>6701324</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120214431</v>
+        <v>120214458</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492819</v>
+        <v>492746</v>
       </c>
       <c r="R6" t="n">
-        <v>6701324</v>
+        <v>6701285</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,9 +1219,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120214376</v>
+        <v>120215561</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1270,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1297,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492819</v>
+        <v>492762</v>
       </c>
       <c r="R7" t="n">
-        <v>6701324</v>
+        <v>6701287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120214458</v>
+        <v>120213970</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1414,13 +1429,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492746</v>
+        <v>492816</v>
       </c>
       <c r="R8" t="n">
-        <v>6701285</v>
+        <v>6701297</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,21 +1462,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1470,26 +1475,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120215561</v>
+        <v>120216601</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,48 +1512,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492762</v>
+        <v>492785</v>
       </c>
       <c r="R9" t="n">
-        <v>6701287</v>
+        <v>6701271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,21 +1569,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1600,6 +1586,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1617,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120214353</v>
+        <v>120214431</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,25 +1630,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,7 +1664,7 @@
         <v>6701324</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,11 +1704,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1724,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120216601</v>
+        <v>120214376</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,38 +1732,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492785</v>
+        <v>492819</v>
       </c>
       <c r="R11" t="n">
-        <v>6701271</v>
+        <v>6701324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,11 +1802,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1814,21 +1829,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120214353</v>
+        <v>120216396</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,34 +924,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492819</v>
+        <v>492762</v>
       </c>
       <c r="R4" t="n">
-        <v>6701324</v>
+        <v>6701287</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,6 +1007,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1015,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120216396</v>
+        <v>120214353</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,43 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492762</v>
+        <v>492819</v>
       </c>
       <c r="R5" t="n">
-        <v>6701287</v>
+        <v>6701324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,21 +1129,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120215290</v>
+        <v>120214353</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492789</v>
+        <v>492819</v>
       </c>
       <c r="R2" t="n">
-        <v>6701247</v>
+        <v>6701324</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,11 +753,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120214276</v>
+        <v>120213970</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,46 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492828</v>
+        <v>492816</v>
       </c>
       <c r="R3" t="n">
-        <v>6701317</v>
+        <v>6701297</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,21 +855,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +868,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1039,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120214353</v>
+        <v>120214376</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,28 +1032,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -1112,9 +1102,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120214458</v>
+        <v>120214276</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,37 +1162,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492746</v>
+        <v>492828</v>
       </c>
       <c r="R6" t="n">
-        <v>6701285</v>
+        <v>6701317</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,22 +1255,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120215561</v>
+        <v>120216601</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,48 +1283,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492762</v>
+        <v>492785</v>
       </c>
       <c r="R7" t="n">
-        <v>6701287</v>
+        <v>6701271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,21 +1340,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1372,6 +1357,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120213970</v>
+        <v>120215290</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,34 +1405,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492816</v>
+        <v>492789</v>
       </c>
       <c r="R8" t="n">
-        <v>6701297</v>
+        <v>6701247</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,6 +1472,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1475,11 +1485,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1496,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120216601</v>
+        <v>120215561</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,34 +1517,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492785</v>
+        <v>492762</v>
       </c>
       <c r="R9" t="n">
-        <v>6701271</v>
+        <v>6701287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,11 +1588,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1586,21 +1615,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1618,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120214431</v>
+        <v>120214458</v>
       </c>
       <c r="B10" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,25 +1644,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,13 +1672,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492819</v>
+        <v>492746</v>
       </c>
       <c r="R10" t="n">
-        <v>6701324</v>
+        <v>6701285</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,9 +1705,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1732,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120214376</v>
+        <v>120214431</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,33 +1760,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -1775,7 +1790,7 @@
         <v>6701324</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,21 +1817,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1825,11 +1830,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120214353</v>
+        <v>120214376</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -748,9 +757,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120213970</v>
+        <v>120214353</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -822,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492816</v>
+        <v>492819</v>
       </c>
       <c r="R3" t="n">
-        <v>6701297</v>
+        <v>6701324</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120216396</v>
+        <v>120216601</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,43 +924,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492762</v>
+        <v>492785</v>
       </c>
       <c r="R4" t="n">
-        <v>6701287</v>
+        <v>6701271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120214376</v>
+        <v>120214458</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,50 +1042,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492819</v>
+        <v>492746</v>
       </c>
       <c r="R5" t="n">
-        <v>6701324</v>
+        <v>6701285</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,21 +1126,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Paula Testad</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1267,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120216601</v>
+        <v>120215290</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,37 +1279,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492785</v>
+        <v>492789</v>
       </c>
       <c r="R7" t="n">
-        <v>6701271</v>
+        <v>6701247</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,6 +1346,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1353,26 +1359,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1389,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120215290</v>
+        <v>120213970</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,39 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492789</v>
+        <v>492816</v>
       </c>
       <c r="R8" t="n">
-        <v>6701247</v>
+        <v>6701297</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1472,11 +1453,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1485,6 +1461,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1501,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120215561</v>
+        <v>120214431</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,55 +1494,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492762</v>
+        <v>492819</v>
       </c>
       <c r="R9" t="n">
-        <v>6701287</v>
+        <v>6701324</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,21 +1555,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1611,11 +1568,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1632,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120214458</v>
+        <v>120216396</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,37 +1600,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492746</v>
+        <v>492762</v>
       </c>
       <c r="R10" t="n">
-        <v>6701285</v>
+        <v>6701287</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1705,21 +1666,11 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1728,26 +1679,46 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Paula Testad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120214431</v>
+        <v>120215561</v>
       </c>
       <c r="B11" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1756,41 +1727,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492819</v>
+        <v>492762</v>
       </c>
       <c r="R11" t="n">
-        <v>6701324</v>
+        <v>6701287</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,11 +1802,21 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1830,6 +1825,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120214376</v>
+        <v>120214353</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -757,19 +748,9 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120214353</v>
+        <v>120214376</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,28 +794,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östervålmyran, Östervålmyran, Dlr</t>
@@ -874,9 +864,19 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 65526-2020 artfynd.xlsx
+++ b/artfynd/A 65526-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>120215290</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
